--- a/Tools/Luban/__table__.xlsx
+++ b/Tools/Luban/__table__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Unity\MiniShip\Tools\Luban\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B94642A-28E5-4856-9B19-F126A41C89E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E0756B-F469-405E-8434-8700855E9955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="226">
   <si>
     <t>##type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ship_speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>loading_speed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,10 +150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>loss_cargo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>货物损失数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -601,10 +593,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Bean.TextAsset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>事件名字</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -889,6 +877,36 @@
   </si>
   <si>
     <t>levels_cargo_capacity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HiddenDeepCanal</t>
+  </si>
+  <si>
+    <t>HiddenShallowCanal</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ship_speed#default=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loading_speed#default=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unloading_speed#default=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loss_cargo#default=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>text</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1227,7 +1245,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1241,22 +1259,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1264,13 +1282,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
         <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
       </c>
       <c r="E5">
         <v>20160</v>
@@ -1278,13 +1296,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -1292,13 +1310,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -1306,41 +1324,41 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
         <v>57</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
         <v>61</v>
       </c>
-      <c r="D9" t="s">
-        <v>63</v>
-      </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10">
         <v>10080</v>
@@ -1348,27 +1366,27 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
         <v>70</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>80640</v>
@@ -1376,13 +1394,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1390,13 +1408,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1404,27 +1422,27 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
       <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
         <v>80</v>
-      </c>
-      <c r="E15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -1432,13 +1450,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E17">
         <v>10080</v>
@@ -1446,13 +1464,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E18">
         <v>0.01</v>
@@ -1460,13 +1478,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -1497,16 +1515,16 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
         <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1514,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
         <v>2</v>
@@ -1536,24 +1554,24 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1564,10 +1582,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1578,10 +1596,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1592,10 +1610,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1606,10 +1624,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1620,10 +1638,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1646,10 +1664,13 @@
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.4140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1663,28 +1684,28 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>222</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="G1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>35</v>
-      </c>
       <c r="K1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1695,31 +1716,31 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
         <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="K2" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1738,28 +1759,28 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" t="s">
-        <v>34</v>
-      </c>
       <c r="J4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -1767,20 +1788,11 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>-0.5</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
         <v>20160</v>
       </c>
@@ -1788,10 +1800,10 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1799,17 +1811,11 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>-1</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
         <v>1</v>
       </c>
@@ -1820,10 +1826,10 @@
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1831,10 +1837,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -1842,9 +1845,6 @@
       <c r="F7">
         <v>-1</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
         <v>20160</v>
       </c>
@@ -1852,10 +1852,10 @@
         <v>20</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1863,20 +1863,11 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>0.5</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
         <v>20160</v>
       </c>
@@ -1884,10 +1875,10 @@
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1914,19 +1905,19 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1937,16 +1928,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1959,30 +1950,30 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
         <v>101</v>
-      </c>
-      <c r="E4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1993,13 +1984,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -2010,13 +2001,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -2027,13 +2018,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -2044,13 +2035,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2061,13 +2052,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -2097,10 +2088,10 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2111,7 +2102,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2124,10 +2115,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2135,7 +2126,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2143,7 +2134,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2168,19 +2159,19 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" t="s">
         <v>114</v>
       </c>
-      <c r="C1" t="s">
-        <v>116</v>
-      </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2213,19 +2204,19 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2307,34 +2298,34 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K1" t="s">
         <v>152</v>
-      </c>
-      <c r="H1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J1" t="s">
-        <v>154</v>
-      </c>
-      <c r="K1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -2342,34 +2333,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2382,54 +2373,54 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" t="s">
         <v>148</v>
       </c>
-      <c r="D4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F4" t="s">
-        <v>151</v>
-      </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" t="s">
         <v>160</v>
       </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" t="s">
-        <v>163</v>
-      </c>
       <c r="G5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H5">
         <v>0.16</v>
@@ -2446,22 +2437,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H6">
         <v>0.16</v>
@@ -2478,22 +2469,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" t="s">
         <v>176</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G7" t="s">
         <v>177</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G7" t="s">
-        <v>180</v>
       </c>
       <c r="H7">
         <v>0.24</v>
@@ -2510,19 +2501,19 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H8">
         <v>0.16</v>
@@ -2545,11 +2536,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF13E1BB-79F3-4DC4-8198-F6C0F9852CF5}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.9140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.25" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -2559,13 +2550,13 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2573,13 +2564,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2592,97 +2583,119 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>141</v>
+        <v>220</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C5:D9" numberStoredAsText="1"/>
+    <ignoredError sqref="C5:D7 C12:C13 D9 D8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2710,31 +2723,31 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1" t="s">
         <v>183</v>
       </c>
-      <c r="G1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I1" t="s">
-        <v>186</v>
-      </c>
       <c r="J1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -2745,31 +2758,31 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J2" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="K2" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2785,31 +2798,31 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I4" t="s">
         <v>192</v>
       </c>
-      <c r="D4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K4" t="s">
         <v>197</v>
-      </c>
-      <c r="H4" t="s">
-        <v>196</v>
-      </c>
-      <c r="I4" t="s">
-        <v>195</v>
-      </c>
-      <c r="J4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2820,28 +2833,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2852,28 +2853,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="J6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2884,28 +2873,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -2916,25 +2893,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
       <c r="J8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2945,25 +2913,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
       <c r="J9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -2974,25 +2933,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
       <c r="J10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -3003,25 +2953,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/Tools/Luban/__table__.xlsx
+++ b/Tools/Luban/__table__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Unity\MiniShip\Tools\Luban\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E0756B-F469-405E-8434-8700855E9955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0197B622-EF4A-4CB1-99B9-8AFF0A7A293F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="key_value" sheetId="3" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="ship" sheetId="8" r:id="rId7"/>
     <sheet name="terrain" sheetId="7" r:id="rId8"/>
     <sheet name="upgrade_award" sheetId="9" r:id="rId9"/>
+    <sheet name="lang" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="294">
   <si>
     <t>##type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -716,10 +717,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ship_smallBoat_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -908,6 +905,256 @@
   <si>
     <t>text</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>en_us</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zh_cn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zh_tw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美式英文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>繁体中文（台湾）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_1_desc</t>
+  </si>
+  <si>
+    <t>event_1_name</t>
+  </si>
+  <si>
+    <t>ship_fast_ship_name</t>
+  </si>
+  <si>
+    <t>ship_freighter_name</t>
+  </si>
+  <si>
+    <t>ship_icebreaker_name</t>
+  </si>
+  <si>
+    <t>upgrade_award_1_desc</t>
+  </si>
+  <si>
+    <t>upgrade_award_1_name</t>
+  </si>
+  <si>
+    <t>普通船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破冰船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ship_small_boat_name</t>
+  </si>
+  <si>
+    <t>ship_small_boat_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_2_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得+1普通船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航线获得了新的普通船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航线获得了新的快速船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得+1快速船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航线获得了新的破冰船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得+1破冰船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得+1货舱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航线获得了新的货舱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得+1港口拓展</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航线获得了港口拓展</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你获得了航线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得+1航线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得+1运河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航线获得了运河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>船速减半</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>en_gb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英式英文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海盗袭击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>船停滞，货物损失1个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>港口罢工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂停装卸货物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风平浪静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风平浪静，船体速度增加50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獲得+1普通船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獲得+1港口拓展</t>
+  </si>
+  <si>
+    <t>你的航綫獲得了新的普通船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獲得+1快速船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航綫獲得了新的快速船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獲得+1破冰船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的航綫獲得了新的破冰船</t>
+  </si>
+  <si>
+    <t>獲得+1貨艙</t>
+  </si>
+  <si>
+    <t>你的航綫獲得了新的貨艙</t>
+  </si>
+  <si>
+    <t>你的航綫獲得了港口拓展</t>
+  </si>
+  <si>
+    <t>獲得+1航綫</t>
+  </si>
+  <si>
+    <t>你獲得了航綫</t>
+  </si>
+  <si>
+    <t>獲得+1運河</t>
+  </si>
+  <si>
+    <t>你的航綫獲得運河</t>
+  </si>
+  <si>
+    <t>暴風雨</t>
+  </si>
+  <si>
+    <t>船速減半</t>
+  </si>
+  <si>
+    <t>海盜襲擊</t>
+  </si>
+  <si>
+    <t>船停滯，貨物損失1個</t>
+  </si>
+  <si>
+    <t>港口把關</t>
+  </si>
+  <si>
+    <t>暫停裝卸貨物</t>
+  </si>
+  <si>
+    <t>風平浪靜</t>
+  </si>
+  <si>
+    <t>風平浪靜，船體速度增加50%</t>
   </si>
 </sst>
 </file>
@@ -1499,6 +1746,375 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78015739-CDE4-42CD-BBBD-3DE16A1B645E}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" t="s">
+        <v>247</v>
+      </c>
+      <c r="D18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C21" t="s">
+        <v>251</v>
+      </c>
+      <c r="D21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D22" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" t="s">
+        <v>254</v>
+      </c>
+      <c r="D23" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" t="s">
+        <v>253</v>
+      </c>
+      <c r="D24" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26" t="s">
+        <v>255</v>
+      </c>
+      <c r="D26" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" t="s">
+        <v>257</v>
+      </c>
+      <c r="D27" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" t="s">
+        <v>258</v>
+      </c>
+      <c r="D28" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" t="s">
+        <v>260</v>
+      </c>
+      <c r="D29" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" t="s">
+        <v>259</v>
+      </c>
+      <c r="D30" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
@@ -1532,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
         <v>142</v>
@@ -1684,16 +2300,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" t="s">
         <v>221</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>222</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>223</v>
-      </c>
-      <c r="G1" t="s">
-        <v>224</v>
       </c>
       <c r="H1" t="s">
         <v>31</v>
@@ -1737,10 +2353,10 @@
         <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1928,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
         <v>142</v>
@@ -1953,7 +2569,7 @@
         <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
         <v>99</v>
@@ -2283,7 +2899,7 @@
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.4140625" customWidth="1"/>
     <col min="5" max="5" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.4140625" bestFit="1" customWidth="1"/>
@@ -2310,7 +2926,7 @@
         <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G1" t="s">
         <v>149</v>
@@ -2333,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
         <v>142</v>
@@ -2388,7 +3004,7 @@
         <v>148</v>
       </c>
       <c r="G4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H4" t="s">
         <v>168</v>
@@ -2472,19 +3088,19 @@
         <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>
       </c>
       <c r="E7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" t="s">
         <v>175</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>176</v>
-      </c>
-      <c r="G7" t="s">
-        <v>177</v>
       </c>
       <c r="H7">
         <v>0.24</v>
@@ -2501,19 +3117,19 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" t="s">
         <v>178</v>
       </c>
-      <c r="C8" t="s">
-        <v>179</v>
-      </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H8">
         <v>0.16</v>
@@ -2630,7 +3246,7 @@
         <v>132</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>138</v>
@@ -2641,7 +3257,7 @@
         <v>133</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>139</v>
@@ -2671,7 +3287,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>138</v>
@@ -2682,7 +3298,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>139</v>
@@ -2729,19 +3345,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G1" t="s">
         <v>180</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>181</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>182</v>
-      </c>
-      <c r="I1" t="s">
-        <v>183</v>
       </c>
       <c r="J1" t="s">
         <v>33</v>
@@ -2764,7 +3380,7 @@
         <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
         <v>48</v>
@@ -2779,10 +3395,10 @@
         <v>48</v>
       </c>
       <c r="J2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2798,31 +3414,31 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" t="s">
         <v>189</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J4" t="s">
         <v>190</v>
       </c>
-      <c r="E4" t="s">
+      <c r="K4" t="s">
         <v>196</v>
-      </c>
-      <c r="F4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" t="s">
-        <v>194</v>
-      </c>
-      <c r="H4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J4" t="s">
-        <v>191</v>
-      </c>
-      <c r="K4" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2836,13 +3452,13 @@
         <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J5" t="s">
+        <v>201</v>
+      </c>
+      <c r="K5" t="s">
         <v>202</v>
-      </c>
-      <c r="K5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2853,16 +3469,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K6" t="s">
         <v>204</v>
-      </c>
-      <c r="K6" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2876,13 +3492,13 @@
         <v>170</v>
       </c>
       <c r="E7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J7" t="s">
+        <v>205</v>
+      </c>
+      <c r="K7" t="s">
         <v>206</v>
-      </c>
-      <c r="K7" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -2899,10 +3515,10 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K8" t="s">
         <v>208</v>
-      </c>
-      <c r="K8" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2919,10 +3535,10 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
+        <v>209</v>
+      </c>
+      <c r="K9" t="s">
         <v>210</v>
-      </c>
-      <c r="K9" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -2939,10 +3555,10 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
+        <v>211</v>
+      </c>
+      <c r="K10" t="s">
         <v>212</v>
-      </c>
-      <c r="K10" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -2959,10 +3575,10 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
+        <v>213</v>
+      </c>
+      <c r="K11" t="s">
         <v>214</v>
-      </c>
-      <c r="K11" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
